--- a/GameData/tables/02_Unit.xlsx
+++ b/GameData/tables/02_Unit.xlsx
@@ -16,12 +16,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_profile" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'unit'!$A$1:$V$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'skill_param'!$A$1:$D$57</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'unit_boost'!$A$1:$G$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'unit'!$A$1:$V$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'skill_param'!$A$1:$D$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'unit_boost'!$A$1:$G$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'unit_levelup'!$A$1:$G$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'unit_star'!$A$1:$D$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'unit_profile'!$A$1:$G$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'unit_profile'!$A$1:$G$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -534,10 +534,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11.6" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -554,11 +554,11 @@
     <col width="12.8" customWidth="1" min="15" max="15"/>
     <col width="12.8" customWidth="1" min="16" max="16"/>
     <col width="15.2" customWidth="1" min="17" max="17"/>
-    <col width="21.2" customWidth="1" min="18" max="18"/>
-    <col width="22.4" customWidth="1" min="19" max="19"/>
-    <col width="21.2" customWidth="1" min="20" max="20"/>
-    <col width="22.4" customWidth="1" min="21" max="21"/>
-    <col width="21.2" customWidth="1" min="22" max="22"/>
+    <col width="23.6" customWidth="1" min="18" max="18"/>
+    <col width="24.8" customWidth="1" min="19" max="19"/>
+    <col width="23.6" customWidth="1" min="20" max="20"/>
+    <col width="24.8" customWidth="1" min="21" max="21"/>
+    <col width="23.6" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1745,8 +1745,328 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>blender</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>800</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="M15" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" s="5" t="inlineStr">
+        <is>
+          <t>unit.blender.name</t>
+        </is>
+      </c>
+      <c r="S15" s="5" t="inlineStr">
+        <is>
+          <t>unit.blender.short</t>
+        </is>
+      </c>
+      <c r="T15" s="5" t="inlineStr">
+        <is>
+          <t>unit.blender.role</t>
+        </is>
+      </c>
+      <c r="U15" s="5" t="inlineStr">
+        <is>
+          <t>unit.blender.skill</t>
+        </is>
+      </c>
+      <c r="V15" s="5" t="inlineStr">
+        <is>
+          <t>unit.blender.desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="M16" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="N16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>unit.purifier.name</t>
+        </is>
+      </c>
+      <c r="S16" s="5" t="inlineStr">
+        <is>
+          <t>unit.purifier.short</t>
+        </is>
+      </c>
+      <c r="T16" s="5" t="inlineStr">
+        <is>
+          <t>unit.purifier.role</t>
+        </is>
+      </c>
+      <c r="U16" s="5" t="inlineStr">
+        <is>
+          <t>unit.purifier.skill</t>
+        </is>
+      </c>
+      <c r="V16" s="5" t="inlineStr">
+        <is>
+          <t>unit.purifier.desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>router</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="N17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" s="5" t="inlineStr">
+        <is>
+          <t>unit.router.name</t>
+        </is>
+      </c>
+      <c r="S17" s="5" t="inlineStr">
+        <is>
+          <t>unit.router.short</t>
+        </is>
+      </c>
+      <c r="T17" s="5" t="inlineStr">
+        <is>
+          <t>unit.router.role</t>
+        </is>
+      </c>
+      <c r="U17" s="5" t="inlineStr">
+        <is>
+          <t>unit.router.skill</t>
+        </is>
+      </c>
+      <c r="V17" s="5" t="inlineStr">
+        <is>
+          <t>unit.router.desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>tv</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="M18" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="N18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" s="5" t="inlineStr">
+        <is>
+          <t>unit.tv.name</t>
+        </is>
+      </c>
+      <c r="S18" s="5" t="inlineStr">
+        <is>
+          <t>unit.tv.short</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>unit.tv.role</t>
+        </is>
+      </c>
+      <c r="U18" s="5" t="inlineStr">
+        <is>
+          <t>unit.tv.skill</t>
+        </is>
+      </c>
+      <c r="V18" s="5" t="inlineStr">
+        <is>
+          <t>unit.tv.desc</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V14"/>
+  <autoFilter ref="A1:V18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1757,10 +2077,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11.6" customWidth="1" min="1" max="1"/>
     <col width="21.2" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="42.8" customWidth="1" min="4" max="4"/>
@@ -2910,8 +3230,388 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>blender</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>execHp</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>마무리: 적 체력이 이 비율 이하면 평타 피해 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>blender</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>execBonus</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>마무리 피해 증가(+70%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>blender</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>grindItvMul</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>분쇄 모드 중 공격 간격 배율</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>blender</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>grindRadius</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>분쇄 모드: 때릴 때 함께 맞는 주변 지상 적 범위(칸)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>airMul</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>공중 적 피해 배율(평타·스킬)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>tick</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>강력 정화 간격(초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>skillDmg</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>강력 정화 1회 피해</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>skillSlow</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>강력 정화 공중 적 둔화율</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>skillSlowSec</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>둔화 시간(초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>router</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>chainN</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>평타가 추가로 튀는 적 수</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>router</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>chainRange</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>튀는 거리(칸)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>router</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>chainDecay</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>튈 때마다 피해 배율</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>router</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>skillChainAdd</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>신호 폭주 중 추가 연쇄</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>router</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>skillItvMul</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>신호 폭주 중 공격 간격 배율</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>router</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>stun</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>신호 폭주 중 맞은 적 기절(초, 보스 1/3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>tv</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>adMin</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>필드 적이 이 수 이상이면 발동(보스가 있으면 바로)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>tv</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>adVuln</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>광고 시간 동안·뒤 받는 피해 증가(방어 감소)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>tv</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>vulnSec</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>받는 피해 증가 지속(초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>tv</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>splashRadius</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>평타 화면 빔 광역 반경(칸)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D57"/>
+  <autoFilter ref="A1:D76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2922,10 +3622,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11.6" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10.4" customWidth="1" min="3" max="3"/>
     <col width="10.4" customWidth="1" min="4" max="4"/>
@@ -3608,8 +4308,208 @@
         <v>0.9</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>blender</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>blender</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>router</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>router</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>tv</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>tv</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G26"/>
+  <autoFilter ref="A1:G34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3945,16 +4845,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="11.6" customWidth="1" min="1" max="1"/>
+    <col width="16.4" customWidth="1" min="2" max="2"/>
     <col width="11.6" customWidth="1" min="3" max="3"/>
     <col width="10.4" customWidth="1" min="4" max="4"/>
-    <col width="24.8" customWidth="1" min="5" max="5"/>
-    <col width="24.8" customWidth="1" min="6" max="6"/>
-    <col width="22.4" customWidth="1" min="7" max="7"/>
+    <col width="27.2" customWidth="1" min="5" max="5"/>
+    <col width="27.2" customWidth="1" min="6" max="6"/>
+    <col width="24.8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4475,8 +5375,156 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>blender</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>art/blender</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>#5FB84A</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>#E9F6E3</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>unit.blender.tagline</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>unit.blender.profile</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>unit.blender.motif</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>art/purifier</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>#3FB6A8</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>#E2F6F3</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>unit.purifier.tagline</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>unit.purifier.profile</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>unit.purifier.motif</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>router</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>art/router</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>#4A68D8</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>#E6ECFB</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>unit.router.tagline</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>unit.router.profile</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>unit.router.motif</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>tv</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>art/tv</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>#E0436B</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>#FCE6EF</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>unit.tv.tagline</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>unit.tv.profile</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>unit.tv.motif</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G14"/>
+  <autoFilter ref="A1:G18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>